--- a/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_10_9_summer.xlsx
+++ b/0_0_Data/3_Naive_Forecaster_Data/1_YoY_Forecast_Vectors/forecast_series_PRIVCON_yoy_AVERAGE_10_9_summer.xlsx
@@ -392,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -414,305 +414,350 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2">
-        <v>39583</v>
+        <v>38496</v>
       </c>
       <c r="B2">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="D2">
-        <v>2009</v>
-      </c>
-      <c r="E2">
-        <v>0.1825419310453436</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2">
-        <v>39948</v>
+        <v>38860</v>
       </c>
       <c r="B3">
-        <v>2009</v>
-      </c>
-      <c r="C3">
-        <v>-0.009261555895478946</v>
+        <v>2006</v>
       </c>
       <c r="D3">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="E3">
-        <v>0.1145211022186787</v>
+        <v>-0.4634751819907912</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2">
-        <v>40310</v>
+        <v>39226</v>
       </c>
       <c r="B4">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="C4">
-        <v>-1.404263945418582</v>
+        <v>2.382020274230801</v>
       </c>
       <c r="D4">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="E4">
-        <v>-0.807808220045203</v>
+        <v>2.023754696885049</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>40676</v>
+        <v>39595</v>
       </c>
       <c r="B5">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="C5">
-        <v>1.692932643509826</v>
+        <v>1.392160100878126</v>
       </c>
       <c r="D5">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="E5">
-        <v>0.6262577107155831</v>
+        <v>1.709158214173456</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>41044</v>
+        <v>39959</v>
       </c>
       <c r="B6">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="C6">
-        <v>1.020829760720687</v>
+        <v>1.012930725088279</v>
       </c>
       <c r="D6">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="E6">
-        <v>1.148272834981245</v>
+        <v>1.682215388696462</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>41409</v>
+        <v>40319</v>
       </c>
       <c r="B7">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="C7">
-        <v>0.6772121200332215</v>
+        <v>2.440553594461403</v>
       </c>
       <c r="D7">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="E7">
-        <v>1.258913537332873</v>
+        <v>2.945546539872113</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>41774</v>
+        <v>40687</v>
       </c>
       <c r="B8">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C8">
-        <v>1.019715257608933</v>
+        <v>1.902195691952047</v>
       </c>
       <c r="D8">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="E8">
-        <v>0.9536145745415947</v>
+        <v>2.594681811711497</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>42137</v>
+        <v>41053</v>
       </c>
       <c r="B9">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C9">
-        <v>2.173959184500363</v>
+        <v>1.553499676054582</v>
       </c>
       <c r="D9">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="E9">
-        <v>1.566646323486065</v>
+        <v>1.311163626693634</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>42503</v>
+        <v>41418</v>
       </c>
       <c r="B10">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C10">
-        <v>1.707434489470039</v>
+        <v>0.6194736285609848</v>
       </c>
       <c r="D10">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="E10">
-        <v>1.30258347990615</v>
+        <v>0.7766551282351042</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>42867</v>
+        <v>41782</v>
       </c>
       <c r="B11">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C11">
-        <v>1.456988786619817</v>
+        <v>0.4902065436673819</v>
       </c>
       <c r="D11">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="E11">
-        <v>1.84279714442821</v>
+        <v>0.7930646576103761</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2">
-        <v>43235</v>
+        <v>42146</v>
       </c>
       <c r="B12">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C12">
-        <v>1.241332692055597</v>
+        <v>1.905689950888578</v>
       </c>
       <c r="D12">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="E12">
-        <v>1.580042106786372</v>
+        <v>1.388683613675679</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2">
-        <v>43600</v>
+        <v>42514</v>
       </c>
       <c r="B13">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C13">
-        <v>1.592885137608979</v>
+        <v>2.68827432811356</v>
       </c>
       <c r="D13">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="E13">
-        <v>1.604795846351492</v>
+        <v>2.207994873007224</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2">
-        <v>43966</v>
+        <v>42878</v>
       </c>
       <c r="B14">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C14">
-        <v>-2.015335584265165</v>
+        <v>1.943557593331668</v>
       </c>
       <c r="D14">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="E14">
-        <v>-1.215549235925817</v>
+        <v>2.830309762977312</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2">
-        <v>44341</v>
+        <v>43244</v>
       </c>
       <c r="B15">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C15">
-        <v>-5.665308402785508</v>
+        <v>1.100325026011384</v>
       </c>
       <c r="D15">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="E15">
-        <v>-4.458023117238186</v>
+        <v>1.734997059187049</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2">
-        <v>44706</v>
+        <v>43608</v>
       </c>
       <c r="B16">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C16">
-        <v>3.55216262984841</v>
+        <v>1.425094261273419</v>
       </c>
       <c r="D16">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="E16">
-        <v>-0.5534294478199198</v>
+        <v>1.138644081307949</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2">
-        <v>45071</v>
+        <v>43976</v>
       </c>
       <c r="B17">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="C17">
-        <v>-1.17492083522599</v>
+        <v>2.190629965965152</v>
       </c>
       <c r="D17">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="E17">
-        <v>0.1140263184959744</v>
+        <v>1.960151128675891</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2">
-        <v>45436</v>
+        <v>44341</v>
       </c>
       <c r="B18">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="C18">
-        <v>0.02017133142706573</v>
+        <v>2.525909494668999</v>
       </c>
       <c r="D18">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="E18">
-        <v>-0.3342090768663986</v>
+        <v>2.956312065996869</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2">
+        <v>44706</v>
+      </c>
+      <c r="B19">
+        <v>2022</v>
+      </c>
+      <c r="C19">
+        <v>0.4613614749821915</v>
+      </c>
+      <c r="D19">
+        <v>2023</v>
+      </c>
+      <c r="E19">
+        <v>2.263499666078128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2">
+        <v>45071</v>
+      </c>
+      <c r="B20">
+        <v>2023</v>
+      </c>
+      <c r="C20">
+        <v>-4.070018373848039</v>
+      </c>
+      <c r="D20">
+        <v>2024</v>
+      </c>
+      <c r="E20">
+        <v>-2.062439327064391</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2">
+        <v>45436</v>
+      </c>
+      <c r="B21">
+        <v>2024</v>
+      </c>
+      <c r="C21">
+        <v>1.033463848836402</v>
+      </c>
+      <c r="D21">
+        <v>2025</v>
+      </c>
+      <c r="E21">
+        <v>0.05482621034866852</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2">
         <v>45800</v>
       </c>
-      <c r="B19">
+      <c r="B22">
         <v>2025</v>
       </c>
-      <c r="C19">
-        <v>0.7917104405398501</v>
-      </c>
-      <c r="D19">
+      <c r="C22">
+        <v>2.298988942566593</v>
+      </c>
+      <c r="D22">
         <v>2026</v>
       </c>
-      <c r="E19">
-        <v>-0.1189552196680155</v>
+      <c r="E22">
+        <v>1.85998739609663</v>
       </c>
     </row>
   </sheetData>
